--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:18:04+00:00</t>
+    <t>2024-03-21T10:58:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1002,7 +1002,7 @@
     <t>Specific specialty associated with the agency | spécialité du professionnel de santé au sein de l'organisation</t>
   </si>
   <si>
-    <t>Specific specialty associated with the agency | spécialité du professionnel de santé au sein de l'organisation.</t>
+    <t>Specific specialty of the practitioner.</t>
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:58:03+00:00</t>
+    <t>2024-03-21T10:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T10:59:21+00:00</t>
+    <t>2024-03-21T12:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T12:49:37+00:00</t>
+    <t>2024-03-21T12:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T12:55:50+00:00</t>
+    <t>2024-03-22T10:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T10:25:22+00:00</t>
+    <t>2024-03-22T13:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/nr-add-profile-list/ig/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T13:38:23+00:00</t>
+    <t>2024-03-25T10:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
